--- a/public/sample_students.xlsx
+++ b/public/sample_students.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
   <si>
     <t>Swarnadeep Biswas</t>
   </si>
@@ -38,9 +38,6 @@
   </si>
   <si>
     <t>D-139,GOVIND PURI MODINAGAR,modinagar,Ghaziabad,Uttar Pradesh,INDIA, Ghaziabad, Uttar Pradesh- 201204</t>
-  </si>
-  <si>
-    <t>reference_no</t>
   </si>
   <si>
     <t>name</t>
@@ -53,7 +50,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="5">
+  <fonts count="4">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -76,13 +73,6 @@
     <font>
       <sz val="10"/>
       <color theme="0"/>
-      <name val="Arial"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
       <name val="Arial"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -123,7 +113,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -135,16 +125,11 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="6">
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
+  <dxfs count="5">
     <dxf>
       <fill>
         <patternFill patternType="none">
@@ -196,10 +181,10 @@
   </dxfs>
   <tableStyles count="1">
     <tableStyle name="Form Responses 1-style" pivot="0" count="4">
-      <tableStyleElement type="wholeTable" size="0" dxfId="5"/>
-      <tableStyleElement type="headerRow" dxfId="4"/>
-      <tableStyleElement type="firstRowStripe" dxfId="3"/>
-      <tableStyleElement type="secondRowStripe" dxfId="2"/>
+      <tableStyleElement type="wholeTable" size="0" dxfId="4"/>
+      <tableStyleElement type="headerRow" dxfId="3"/>
+      <tableStyleElement type="firstRowStripe" dxfId="2"/>
+      <tableStyleElement type="secondRowStripe" dxfId="1"/>
     </tableStyle>
   </tableStyles>
 </styleSheet>
@@ -210,14 +195,11 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Form_Responses" displayName="Form_Responses" ref="A1:C5" headerRowDxfId="1">
-  <autoFilter ref="A1:C5">
-    <filterColumn colId="2"/>
-  </autoFilter>
-  <tableColumns count="3">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Form_Responses" displayName="Form_Responses" ref="A1:B5" headerRowDxfId="0">
+  <autoFilter ref="A1:B5"/>
+  <tableColumns count="2">
     <tableColumn id="3" name="name"/>
     <tableColumn id="4" name="address"/>
-    <tableColumn id="1" name="reference_no" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="Form Responses 1-style" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -424,65 +406,52 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:B5"/>
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col min="1" max="8" width="18.85546875" customWidth="1"/>
+    <col min="1" max="1" width="18.85546875" customWidth="1"/>
+    <col min="2" max="2" width="122" bestFit="1" customWidth="1"/>
+    <col min="3" max="7" width="18.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" s="3" customFormat="1" ht="22.5" customHeight="1" thickBot="1">
+    <row r="1" spans="1:2" s="3" customFormat="1" ht="22.5" customHeight="1" thickBot="1">
       <c r="A1" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B1" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="B1" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C1" s="5" t="s">
-        <v>8</v>
-      </c>
     </row>
-    <row r="2" spans="1:3" ht="22.5" customHeight="1" thickBot="1">
+    <row r="2" spans="1:2" ht="22.5" customHeight="1" thickBot="1">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="6">
-        <v>1</v>
-      </c>
     </row>
-    <row r="3" spans="1:3" ht="22.5" customHeight="1" thickBot="1">
+    <row r="3" spans="1:2" ht="22.5" customHeight="1" thickBot="1">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="6">
-        <v>2</v>
-      </c>
     </row>
-    <row r="4" spans="1:3" ht="22.5" customHeight="1" thickBot="1">
+    <row r="4" spans="1:2" ht="22.5" customHeight="1" thickBot="1">
       <c r="A4" s="1" t="s">
         <v>2</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="6">
-        <v>3</v>
-      </c>
     </row>
-    <row r="5" spans="1:3" ht="22.5" customHeight="1" thickBot="1">
+    <row r="5" spans="1:2" ht="22.5" customHeight="1" thickBot="1">
       <c r="A5" s="1" t="s">
         <v>3</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>7</v>
-      </c>
-      <c r="C5" s="6">
-        <v>4</v>
       </c>
     </row>
   </sheetData>
